--- a/file.xlsx
+++ b/file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mainak\result-seed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145125C1-F525-4910-A586-54956B75CC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA1FE19-574E-4D46-9ED0-B480F1B2A8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{A5DF20CB-55F0-4F68-A430-D58D5BAD753E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t>userId</t>
   </si>
@@ -62,17 +62,6 @@
     "type": "application/pdf"
   }
 ]</t>
-  </si>
-  <si>
-    <t>[
-  {
-    "link": "https://del1.vultrobjects.com/crmtest/CRM/resultAnalysis/acbd6f65-8af7-495b-b0b3-a859615fdd41_93.pdf",
-    "type": "application/pdf"
-  }
-]</t>
-  </si>
-  <si>
-    <t>c</t>
   </si>
 </sst>
 </file>
@@ -476,16 +465,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>596</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C5" s="2"/>

--- a/file.xlsx
+++ b/file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mainak\result-seed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA1FE19-574E-4D46-9ED0-B480F1B2A8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C168079C-2360-465C-9FD9-2F239C3A55AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{A5DF20CB-55F0-4F68-A430-D58D5BAD753E}"/>
   </bookViews>
@@ -50,15 +50,15 @@
   <si>
     <t>[
   {
-    "link": "https://del1.vultrobjects.com/crmaswinibajaj/CRM/resultAnalysis/4f675442-e6c5-4425-8d2c-920a0ef0920c_8.pdf",
+    "link": "https://del1.vultrobjects.com/crmtest/CRM/resultAnalysis/e80c6b61-ab53-47f2-aa34-901cb4d540b0_24.pdf",
     "type": "application/pdf"
   }
-]</t>
+]+C2</t>
   </si>
   <si>
     <t>[
   {
-    "link": "https://del1.vultrobjects.com/crmaswinibajaj/CRM/resultAnalysis/ebbda1e5-c434-44c9-a2ec-c32ff6e97c49_8.pdf",
+    "link": "https://del1.vultrobjects.com/crmaswinibajaj/CRM/resultAnalysis/a679b1b0-25c6-4c09-9224-92046fdaef83_98.pdf",
     "type": "application/pdf"
   }
 ]</t>
@@ -451,7 +451,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
@@ -462,7 +462,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
